--- a/artfynd/A 44608-2020 artfynd.xlsx
+++ b/artfynd/A 44608-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44608-2020 artfynd.xlsx
+++ b/artfynd/A 44608-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4170477</v>
+        <v>111746</v>
       </c>
       <c r="B2" t="n">
-        <v>95510</v>
+        <v>108122</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Krypfloka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Helosciadium inundatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) W. D. J. Koch</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bö tjärns sydöstra strand V om Pumpstation, Boh</t>
+          <t>Tjörn, Bö tjärn, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>298843.8467798341</v>
+        <v>299020.5286865672</v>
       </c>
       <c r="R2" t="n">
-        <v>6430890.968758829</v>
+        <v>6430900.664760527</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +759,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-07-24</t>
+          <t>2012-08-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -755,7 +769,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-07-24</t>
+          <t>2012-08-11</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -774,152 +788,21 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>hällmark</t>
+          <t>Strandant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Henrik Wegnelius</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Föreningen Bohusläns Flora</t>
+          <t>Henrik Wegnelius</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>111746</v>
-      </c>
-      <c r="B3" t="n">
-        <v>108122</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>79</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Krypfloka</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Helosciadium inundatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) W. D. J. Koch</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tjörn, Bö tjärn, Boh</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>299020.5286865672</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6430900.664760527</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tjörn</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Stenkyrka</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2012-08-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2012-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Strandant</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Henrik Wegnelius</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Henrik Wegnelius</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
